--- a/www/terminologies/CodeSystem-tre-r396-autorite.xlsx
+++ b/www/terminologies/CodeSystem-tre-r396-autorite.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r396-autorite</t>
+    <t>http://example.org/CodeSystem/tre-r396-autorite</t>
   </si>
   <si>
     <t>Identifier</t>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260629120000</t>
+    <t>20260928120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:00:00+01:00</t>
+    <t>2026-09-28T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
